--- a/JsonConverter/JsonConverter/ExcelFiles/Monster.xlsx
+++ b/JsonConverter/JsonConverter/ExcelFiles/Monster.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.12458"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.12641"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\unityprojects\Oz6-TeamPortfolio3D_RPG\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\unityprojects\Oz6-TeamPortfolio3D_RPG\JsonConverter\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -19,12 +19,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <x:si>
     <x:t>DetectRange</x:t>
   </x:si>
   <x:si>
-    <x:t>BaseAttack</x:t>
+    <x:t>mob_skeleton</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1층에서 출현하는 몹이다</x:t>
   </x:si>
   <x:si>
     <x:t>테스트용 몹이다.</x:t>
@@ -36,43 +39,28 @@
     <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
+    <x:t>BaseAttack</x:t>
   </x:si>
   <x:si>
-    <x:t>PrefabPath</x:t>
+    <x:t>DropEXP</x:t>
   </x:si>
   <x:si>
-    <x:t>MoveSpeed</x:t>
+    <x:t>기본 체력</x:t>
   </x:si>
   <x:si>
-    <x:t>StopDistance</x:t>
+    <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>플레이어와 유지하는 거리</x:t>
+    <x:t>float</x:t>
   </x:si>
   <x:si>
-    <x:t>mob_goblin_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고블린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+    <x:t>몬스터의 이름</x:t>
   </x:si>
   <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
     <x:t>감지 거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터의 이름</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
@@ -84,25 +72,46 @@
     <x:t>이동속도</x:t>
   </x:si>
   <x:si>
-    <x:t>공격 사거리</x:t>
-  </x:si>
-  <x:si>
     <x:t>몬스터 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
   </x:si>
   <x:si>
     <x:t>BaseHp</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
+    <x:t>공격 사거리</x:t>
   </x:si>
   <x:si>
-    <x:t>DropEXP</x:t>
+    <x:t>mob_goblin_1</x:t>
   </x:si>
   <x:si>
-    <x:t>기본 체력</x:t>
+    <x:t>StopDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플레이어와 유지하는 거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고블린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스켈레톤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoveSpeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -249,7 +258,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -301,11 +310,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -933,136 +939,136 @@
   <x:sheetData>
     <x:row r="1" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="D1" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I1" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H1" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I1" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="K1" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="13.199999999999999">
       <x:c r="A2" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I2" s="15" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J2" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="13" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C3" s="13" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="14" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J3" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K3" s="13" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16384" s="16" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A4" s="18" t="s">
+      <x:c r="A4" s="5" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="5">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F4" s="5">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B4" s="18" t="s">
-        <x:v>12</x:v>
+      <x:c r="G4" s="5">
+        <x:v>5</x:v>
       </x:c>
-      <x:c r="C4" s="18" t="s">
-        <x:v>2</x:v>
+      <x:c r="H4" s="5">
+        <x:v>5</x:v>
       </x:c>
-      <x:c r="D4" s="11"/>
-      <x:c r="E4" s="18">
-        <x:v>100</x:v>
+      <x:c r="I4" s="15">
+        <x:v>1</x:v>
       </x:c>
-      <x:c r="F4" s="18">
+      <x:c r="J4" s="17">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G4" s="18">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H4" s="18">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I4" s="17">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J4" s="4">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K4" s="18">
+      <x:c r="K4" s="5">
         <x:v>0.80000000000000004</x:v>
       </x:c>
       <x:c r="P4" s="4"/>
@@ -17436,15 +17442,37 @@
       <x:c r="XFD4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:11" ht="15.75" customHeight="1">
-      <x:c r="A5" s="5"/>
-      <x:c r="B5" s="6"/>
-      <x:c r="C5" s="6"/>
-      <x:c r="D5" s="11"/>
-      <x:c r="E5" s="6"/>
-      <x:c r="F5" s="6"/>
-      <x:c r="G5" s="6"/>
-      <x:c r="H5" s="6"/>
-      <x:c r="K5" s="6"/>
+      <x:c r="A5" s="5" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D5" s="2"/>
+      <x:c r="E5" s="6">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F5" s="6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G5" s="6">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H5" s="6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I5" s="15">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J5" s="17">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K5" s="6">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A6" s="6"/>

--- a/JsonConverter/JsonConverter/ExcelFiles/Monster.xlsx
+++ b/JsonConverter/JsonConverter/ExcelFiles/Monster.xlsx
@@ -21,13 +21,76 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <x:si>
-    <x:t>DetectRange</x:t>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고블린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격 사거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스켈레톤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터의 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropEXP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감지 거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이동속도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 체력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_goblin_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StopDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1층에서 출현하는 몹이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플레이어와 유지하는 거리</x:t>
   </x:si>
   <x:si>
     <x:t>mob_skeleton</x:t>
   </x:si>
   <x:si>
-    <x:t>1층에서 출현하는 몹이다</x:t>
+    <x:t>DetectRange</x:t>
   </x:si>
   <x:si>
     <x:t>테스트용 몹이다.</x:t>
@@ -36,73 +99,10 @@
     <x:t>AttackRange</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
     <x:t>BaseAttack</x:t>
   </x:si>
   <x:si>
-    <x:t>DropEXP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 체력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터의 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감지 거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 공격력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이동속도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격 사거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_goblin_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StopDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플레이어와 유지하는 거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고블린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스켈레톤</x:t>
+    <x:t>Description</x:t>
   </x:si>
   <x:si>
     <x:t>캐릭터 고유 ID</x:t>
@@ -942,112 +942,112 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I1" s="15" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K1" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="13.199999999999999">
       <x:c r="A2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="s">
+      <x:c r="H2" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D2" s="2" t="s">
+      <x:c r="I2" s="15" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I2" s="15" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="J2" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="13" t="s">
-        <x:v>23</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="13" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="13" t="s">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I3" s="14" t="s">
-        <x:v>4</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J3" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K3" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16384" s="16" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="5">
@@ -1063,13 +1063,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I4" s="15">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J4" s="17">
         <x:v>10</x:v>
       </x:c>
       <x:c r="K4" s="5">
-        <x:v>0.80000000000000004</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="P4" s="4"/>
       <x:c r="Q4" s="4"/>
@@ -17443,13 +17443,13 @@
     </x:row>
     <x:row r="5" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="6">
